--- a/JUGADORES T5.xlsx
+++ b/JUGADORES T5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1374E3BE-D9C7-4FC4-ADB9-A1927CF76C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553594A2-57E5-4C81-8774-E2DE39BFD72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{A98060DC-1932-43E6-9169-0378406E7D7E}"/>
   </bookViews>
@@ -123,10 +123,10 @@
     <t>Leo Garrido</t>
   </si>
   <si>
-    <t>Álvaro Monleon</t>
-  </si>
-  <si>
     <t>Alex Navarro</t>
+  </si>
+  <si>
+    <t>Álvaro Monleón</t>
   </si>
 </sst>
 </file>
@@ -553,7 +553,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -578,7 +578,7 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
